--- a/Vf/TABLE_4_5/Table_5_PanelB_Multiplicative_MIDAS.xlsx
+++ b/Vf/TABLE_4_5/Table_5_PanelB_Multiplicative_MIDAS.xlsx
@@ -484,13 +484,13 @@
         <v>1.066307115192855</v>
       </c>
       <c r="C4" t="n">
-        <v>1.148976373689262</v>
+        <v>1.148681918517166</v>
       </c>
       <c r="D4" t="n">
-        <v>1.128473264335124</v>
+        <v>1.127693539982277</v>
       </c>
       <c r="E4" t="n">
-        <v>1.03900982772799</v>
+        <v>1.038515774125469</v>
       </c>
     </row>
     <row r="5">
@@ -515,10 +515,10 @@
         <v>0.95</v>
       </c>
       <c r="B6" t="n">
-        <v>0.952792009624518</v>
+        <v>0.9245452218414361</v>
       </c>
       <c r="C6" t="n">
-        <v>1.036255221738639</v>
+        <v>1.035461354662676</v>
       </c>
       <c r="D6" t="n">
         <v>1.067643879041825</v>
